--- a/data/trans_dic/Q20C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,52</t>
+          <t>0,0; 67,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 60,39</t>
+          <t>12,76; 60,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 50,32</t>
+          <t>6,42; 49,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 36,81</t>
+          <t>4,4; 39,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 58,9</t>
+          <t>7,63; 57,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,96</t>
+          <t>0,0; 32,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 50,15</t>
+          <t>6,55; 54,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 50,38</t>
+          <t>7,83; 48,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 45,02</t>
+          <t>5,8; 49,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 38,47</t>
+          <t>8,98; 35,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 43,42</t>
+          <t>10,06; 40,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 34,29</t>
+          <t>8,9; 35,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,71; 64,94</t>
+          <t>13,34; 64,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,83</t>
+          <t>0,0; 54,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 61,83</t>
+          <t>10,99; 65,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,25</t>
+          <t>0,0; 45,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 62,07</t>
+          <t>18,35; 61,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 64,07</t>
+          <t>7,72; 63,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,66</t>
+          <t>0,0; 17,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,03</t>
+          <t>0,0; 25,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,5; 55,65</t>
+          <t>21,44; 54,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 47,21</t>
+          <t>10,12; 46,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 36,46</t>
+          <t>6,33; 34,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 80,46</t>
+          <t>11,81; 79,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,98</t>
+          <t>0,0; 59,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,49</t>
+          <t>0,0; 48,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 45,96</t>
+          <t>5,92; 46,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 57,62</t>
+          <t>11,71; 57,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 54,69</t>
+          <t>6,81; 58,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 63,39</t>
+          <t>8,5; 60,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 50,95</t>
+          <t>14,27; 50,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 33,3</t>
+          <t>5,99; 34,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 43,94</t>
+          <t>7,72; 47,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 39,79</t>
+          <t>7,38; 43,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 64,94</t>
+          <t>14,36; 64,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,61</t>
+          <t>0,0; 27,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 57,96</t>
+          <t>7,24; 58,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,51; 60,98</t>
+          <t>19,02; 61,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,15</t>
+          <t>0,0; 36,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 49,69</t>
+          <t>10,0; 49,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 52,63</t>
+          <t>9,9; 53,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 43,18</t>
+          <t>8,49; 41,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 41,68</t>
+          <t>7,58; 42,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 35,44</t>
+          <t>6,44; 32,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 44,14</t>
+          <t>13,58; 44,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 47,34</t>
+          <t>18,62; 45,84</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 43,79</t>
+          <t>13,46; 42,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 30,79</t>
+          <t>10,33; 31,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 38,72</t>
+          <t>11,27; 35,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 40,07</t>
+          <t>16,52; 38,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 30,04</t>
+          <t>9,32; 30,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 37,77</t>
+          <t>17,77; 37,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,48</t>
+          <t>15,44; 38,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 29,07</t>
+          <t>11,39; 29,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,44</t>
+          <t>13,58; 31,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,01; 32,48</t>
+          <t>17,14; 31,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,72; 33,58</t>
+          <t>17,33; 34,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 30,9</t>
+          <t>16,36; 30,6</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 3942</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1949; 8934</t>
+          <t>1888; 8963</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1097; 8782</t>
+          <t>1120; 8608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>483; 5161</t>
+          <t>617; 5489</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>887; 6536</t>
+          <t>847; 6353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6017</t>
+          <t>0; 6197</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>836; 6455</t>
+          <t>843; 7038</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>840; 5454</t>
+          <t>848; 5217</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>970; 7610</t>
+          <t>981; 8435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3014; 12935</t>
+          <t>3019; 12086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3204; 13168</t>
+          <t>3052; 12264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1867; 8520</t>
+          <t>2212; 8818</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1585</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2045; 9683</t>
+          <t>1989; 9639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6299</t>
+          <t>0; 6146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1132; 6798</t>
+          <t>1209; 7220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4082</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5034; 15895</t>
+          <t>4698; 15741</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1047; 8691</t>
+          <t>1047; 8630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>0; 1831</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5073</t>
+          <t>0; 4033</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8305; 22548</t>
+          <t>8687; 22276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2920; 11730</t>
+          <t>2514; 11504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1621; 7882</t>
+          <t>1368; 7529</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>993; 6846</t>
+          <t>1005; 6797</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2175</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6819</t>
+          <t>0; 6795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6457</t>
+          <t>0; 6857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>983; 7695</t>
+          <t>991; 7856</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1891; 9974</t>
+          <t>2027; 9885</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>861; 7027</t>
+          <t>875; 7534</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>576; 4422</t>
+          <t>593; 4240</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3510; 12868</t>
+          <t>3603; 12838</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1828; 10757</t>
+          <t>1934; 11189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1063; 10642</t>
+          <t>1870; 11597</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1482; 8424</t>
+          <t>1561; 9187</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1753; 7908</t>
+          <t>1748; 7902</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>772; 6476</t>
+          <t>809; 6484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3769; 10686</t>
+          <t>3332; 10762</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>0; 4422</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1914; 9648</t>
+          <t>1942; 9589</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2255; 11031</t>
+          <t>2075; 11246</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1463; 6718</t>
+          <t>1322; 6461</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1861; 10139</t>
+          <t>1843; 10452</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2895; 12225</t>
+          <t>2221; 11344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4165; 14185</t>
+          <t>4363; 14280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6440; 15659</t>
+          <t>6161; 15163</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4680; 14587</t>
+          <t>4484; 14136</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5604; 18409</t>
+          <t>6173; 18557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6087; 19857</t>
+          <t>5778; 18392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9714; 22730</t>
+          <t>9372; 21865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3990; 14723</t>
+          <t>4570; 14833</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14580; 30653</t>
+          <t>14419; 30731</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9952; 23784</t>
+          <t>9300; 23282</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4944; 12785</t>
+          <t>5009; 12850</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11208; 25061</t>
+          <t>11181; 26193</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23978; 45776</t>
+          <t>24158; 44475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18642; 37453</t>
+          <t>19332; 38315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15738; 31122</t>
+          <t>16474; 30813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q20C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,87</t>
+          <t>0,0; 67,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 60,59</t>
+          <t>13,24; 60,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 49,32</t>
+          <t>6,24; 48,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 39,15</t>
+          <t>3,21; 35,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 57,25</t>
+          <t>7,88; 56,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,92</t>
+          <t>0,0; 32,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 54,68</t>
+          <t>6,54; 56,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 48,19</t>
+          <t>7,05; 47,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 49,9</t>
+          <t>5,78; 49,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 35,95</t>
+          <t>9,09; 38,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 40,44</t>
+          <t>10,05; 40,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 35,49</t>
+          <t>8,48; 35,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 64,64</t>
+          <t>12,92; 64,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,47</t>
+          <t>0,0; 55,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 65,66</t>
+          <t>17,99; 72,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,09</t>
+          <t>0,0; 44,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 61,47</t>
+          <t>19,8; 59,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 63,63</t>
+          <t>8,06; 60,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,24</t>
+          <t>0,0; 21,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,46</t>
+          <t>0,0; 28,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,44; 54,98</t>
+          <t>20,45; 53,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 46,3</t>
+          <t>8,79; 46,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 34,83</t>
+          <t>11,1; 46,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 79,88</t>
+          <t>11,76; 79,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,77</t>
+          <t>0,0; 59,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,31</t>
+          <t>0,0; 44,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 46,91</t>
+          <t>5,82; 47,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 57,11</t>
+          <t>11,41; 59,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 58,63</t>
+          <t>6,71; 52,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 60,79</t>
+          <t>12,48; 66,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 50,84</t>
+          <t>12,19; 48,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 34,64</t>
+          <t>6,13; 35,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 47,88</t>
+          <t>4,54; 44,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 43,4</t>
+          <t>9,44; 41,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 64,89</t>
+          <t>13,97; 64,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,11</t>
+          <t>0,0; 27,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 58,03</t>
+          <t>7,01; 59,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 61,42</t>
+          <t>20,44; 58,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,39</t>
+          <t>0,0; 40,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 49,38</t>
+          <t>10,11; 48,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 53,65</t>
+          <t>10,4; 52,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 41,53</t>
+          <t>7,87; 38,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 42,96</t>
+          <t>10,56; 42,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 32,88</t>
+          <t>6,25; 32,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 44,44</t>
+          <t>13,58; 44,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 45,84</t>
+          <t>16,68; 42,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 42,44</t>
+          <t>13,49; 44,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 31,04</t>
+          <t>10,52; 32,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 35,87</t>
+          <t>11,01; 35,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 38,54</t>
+          <t>18,9; 40,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 30,26</t>
+          <t>8,32; 30,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,77; 37,86</t>
+          <t>17,42; 37,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,44; 38,64</t>
+          <t>16,25; 39,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 29,22</t>
+          <t>12,33; 28,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,82</t>
+          <t>13,24; 31,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 31,56</t>
+          <t>16,95; 31,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,35</t>
+          <t>17,23; 33,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,36; 30,6</t>
+          <t>17,57; 33,27</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>5027</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 3897</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1888; 8963</t>
+          <t>1959; 8983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1120; 8608</t>
+          <t>1088; 8500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>617; 5489</t>
+          <t>463; 5083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>847; 6353</t>
+          <t>875; 6233</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6197</t>
+          <t>0; 6153</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>843; 7038</t>
+          <t>842; 7225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>848; 5217</t>
+          <t>887; 5990</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>981; 8435</t>
+          <t>977; 8308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3019; 12086</t>
+          <t>3058; 12966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3052; 12264</t>
+          <t>3048; 12280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2212; 8818</t>
+          <t>2290; 9562</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>467</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>6829</t>
         </is>
       </c>
     </row>
@@ -1858,57 +1858,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1989; 9639</t>
+          <t>1927; 9607</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6146</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1209; 7220</t>
+          <t>2587; 10479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 4022</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4698; 15741</t>
+          <t>5071; 15265</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1047; 8630</t>
+          <t>1093; 8183</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1831</t>
+          <t>0; 2532</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4033</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8687; 22276</t>
+          <t>8287; 21632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2514; 11504</t>
+          <t>2184; 11538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1368; 7529</t>
+          <t>2911; 12303</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>5558</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1005; 6797</t>
+          <t>1001; 6764</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2071,52 +2071,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6795</t>
+          <t>0; 6751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6857</t>
+          <t>0; 6909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>991; 7856</t>
+          <t>975; 7901</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2027; 9885</t>
+          <t>1976; 10228</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>875; 7534</t>
+          <t>863; 6800</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>593; 4240</t>
+          <t>1146; 6075</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3603; 12838</t>
+          <t>3078; 12154</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1934; 11189</t>
+          <t>1982; 11309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1870; 11597</t>
+          <t>1101; 10760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1561; 9187</t>
+          <t>2325; 10248</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10632</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1748; 7902</t>
+          <t>1701; 7850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>809; 6484</t>
+          <t>784; 6624</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3332; 10762</t>
+          <t>3739; 10788</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1942; 9589</t>
+          <t>1964; 9369</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2075; 11246</t>
+          <t>2180; 11059</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1322; 6461</t>
+          <t>1366; 6606</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1843; 10452</t>
+          <t>2568; 10375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2221; 11344</t>
+          <t>2155; 11315</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4363; 14280</t>
+          <t>4363; 14409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6161; 15163</t>
+          <t>5946; 15130</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4484; 14136</t>
+          <t>4492; 14910</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6173; 18557</t>
+          <t>6287; 19299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5778; 18392</t>
+          <t>5647; 18297</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9372; 21865</t>
+          <t>11824; 25634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4570; 14833</t>
+          <t>4076; 14980</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14419; 30731</t>
+          <t>14137; 30575</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9300; 23282</t>
+          <t>9792; 23513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5009; 12850</t>
+          <t>6284; 14721</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11181; 26193</t>
+          <t>10902; 25698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24158; 44475</t>
+          <t>23894; 44613</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19332; 38315</t>
+          <t>19221; 37717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16474; 30813</t>
+          <t>19951; 37767</t>
         </is>
       </c>
     </row>
